--- a/data/trans_camb/P19C08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,2</t>
+          <t>-2,36; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,29</t>
+          <t>-2,5; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,0</t>
+          <t>-3,48; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,44</t>
+          <t>-2,18; 1,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,0</t>
+          <t>-3,12; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-3,21; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,92</t>
+          <t>-1,62; 0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,37</t>
+          <t>-1,96; 0,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,25</t>
+          <t>-2,35; -0,25</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,07</t>
+          <t>0,0; 0,08</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,26</t>
+          <t>0,34; 3,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,78</t>
+          <t>-0,82; 1,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,86</t>
+          <t>-0,8; 1,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,86</t>
+          <t>0,02; 1,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,21</t>
+          <t>-0,45; 1,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,18</t>
+          <t>-0,88; 0,18</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,57</t>
+          <t>-0,44; 3,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,0</t>
+          <t>-2,05; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,07; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,75</t>
+          <t>-0,17; 1,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,0</t>
+          <t>-1,01; 0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,0</t>
+          <t>-0,94; 0,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-3,11; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-2,95; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,18</t>
+          <t>-1,6; 1,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-3,22; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,13</t>
+          <t>-2,95; 0,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>-2,39; -0,26</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>-2,28; -0,26</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; -0,26</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,81</t>
+          <t>-1,35; 0,83</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 386,33</t>
+          <t>-87,45; —</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,87</t>
+          <t>-0,28; 4,29</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-2,92; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,53</t>
+          <t>-2,32; 0,53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,4</t>
+          <t>-0,17; 2,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,01</t>
+          <t>-0,78; 0,88</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,88</t>
+          <t>-0,2; 1,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1983,37 +1983,37 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,96</t>
+          <t>0,16; 3,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,4</t>
+          <t>-1,22; 0,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,51</t>
+          <t>-0,74; 1,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,11</t>
+          <t>-0,9; 0,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,72</t>
+          <t>-0,42; 0,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,65</t>
+          <t>-0,57; 0,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,48</t>
+          <t>-0,1; 1,52</t>
         </is>
       </c>
     </row>
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,28; —</t>
+          <t>-81,98; 499,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-84,58; 522,42</t>
+          <t>-77,25; 947,19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 666,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 845,56</t>
+          <t>-33,64; 985,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,81</t>
+          <t>-1,04; 0,93</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; -0,18</t>
+          <t>-1,6; -0,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,71</t>
+          <t>-1,25; 0,68</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,28</t>
+          <t>-1,52; 0,38</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,09; -0,31</t>
+          <t>-2,04; -0,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,54</t>
+          <t>-1,41; 0,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,31</t>
+          <t>-1,01; 0,3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; -0,41</t>
+          <t>-1,56; -0,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,4</t>
+          <t>-0,97; 0,35</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-85,09; 445,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-84,45; 309,02</t>
+          <t>-88,3; 294,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 151,36</t>
+          <t>-100,0; 235,1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-82,82; 199,06</t>
+          <t>-85,28; 212,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 84,28</t>
+          <t>-81,19; 85,91</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 102,65</t>
+          <t>-70,96; 91,62</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,76</t>
+          <t>-0,1; 0,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,08</t>
+          <t>-0,48; 0,07</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,5</t>
+          <t>-0,2; 0,52</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,47</t>
+          <t>-0,33; 0,48</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; -0,02</t>
+          <t>-0,7; 0,01</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,16</t>
+          <t>-0,55; 0,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,45</t>
+          <t>-0,13; 0,46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; -0,05</t>
+          <t>-0,52; -0,05</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,21</t>
+          <t>-0,28; 0,21</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 394,86</t>
+          <t>-26,28; 324,15</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-92,62; 58,92</t>
+          <t>-87,75; 71,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 280,4</t>
+          <t>-45,72; 263,85</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 130,68</t>
+          <t>-44,4; 144,62</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 5,38</t>
+          <t>-89,02; 18,05</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 49,69</t>
+          <t>-67,82; 47,09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 137,44</t>
+          <t>-23,38; 149,22</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-83,67; -10,35</t>
+          <t>-84,12; -5,29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 65,62</t>
+          <t>-48,33; 64,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,06</t>
+          <t>-2,46; 1,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,31</t>
+          <t>-2,08; 1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,0</t>
+          <t>-3,51; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,48</t>
+          <t>-2,18; 1,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,0</t>
+          <t>-3,13; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,88</t>
+          <t>-1,67; 0,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,29</t>
+          <t>-1,85; 0,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,25</t>
+          <t>-2,27; -0,25</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,94; 372,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,19</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,08</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,35</t>
+          <t>0,33; 3,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,78</t>
+          <t>-0,8; 1,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,91</t>
+          <t>-0,8; 1,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,34</t>
+          <t>-1,81; 0,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,9</t>
+          <t>0,04; 1,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,08</t>
+          <t>-0,44; 1,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,18</t>
+          <t>-1,0; 0,18</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-57,32%</t>
+          <t>-57,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-59,1%</t>
+          <t>-59,19%</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,89</t>
+          <t>-0,45; 3,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,96</t>
+          <t>-0,14; 1,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>-2,41; 0,0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>-3,11; 0,0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-2,95; 0,0</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,2</t>
+          <t>-1,62; 1,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-3,7; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,95</t>
+          <t>-2,82; 0,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; -0,26</t>
+          <t>-2,2; -0,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,26</t>
+          <t>-2,16; -0,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,83</t>
+          <t>-1,52; 0,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,59%</t>
+          <t>-23,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,06%</t>
+          <t>-13,9%</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-87,45; —</t>
+          <t>-87,76; 277,14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,29</t>
+          <t>-0,38; 4,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,0</t>
+          <t>-3,24; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,53</t>
+          <t>-2,41; 0,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,64</t>
+          <t>-0,12; 2,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,88</t>
+          <t>-0,71; 0,91</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-54,05%</t>
+          <t>-56,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,73</t>
+          <t>-0,19; 1,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-0,97; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,12</t>
+          <t>0,29; 3,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,42</t>
+          <t>-1,22; 0,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,57</t>
+          <t>-0,75; 1,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,97</t>
+          <t>-0,56; 1,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,78</t>
+          <t>-0,44; 0,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,62</t>
+          <t>-0,53; 0,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,52</t>
+          <t>0,11; 1,79</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>549,82%</t>
+          <t>643,65%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>135,82%</t>
+          <t>198,63%</t>
         </is>
       </c>
     </row>
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-81,98; 499,53</t>
+          <t>-64,21; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-77,25; 947,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 666,48</t>
+          <t>-100,0; 516,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 985,03</t>
+          <t>-24,66; 1356,8</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,93</t>
+          <t>-0,91; 0,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; -0,17</t>
+          <t>-1,72; -0,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,68</t>
+          <t>-0,91; 0,92</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,38</t>
+          <t>-1,76; 0,3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,31</t>
+          <t>-2,14; -0,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,54</t>
+          <t>-1,38; 0,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,3</t>
+          <t>-1,07; 0,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; -0,39</t>
+          <t>-1,58; -0,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,35</t>
+          <t>-0,91; 0,45</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-19,26%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-28,53%</t>
+          <t>-30,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-26,02%</t>
+          <t>-15,15%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,95; 633,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 294,23</t>
+          <t>-77,32; 454,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 235,1</t>
+          <t>-100,0; 185,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 212,1</t>
+          <t>-83,1; 187,05</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 85,91</t>
+          <t>-80,58; 88,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 91,62</t>
+          <t>-69,33; 102,51</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,68</t>
+          <t>-0,06; 0,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,07</t>
+          <t>-0,49; 0,05</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,52</t>
+          <t>-0,16; 0,59</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,48</t>
+          <t>-0,29; 0,46</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,01</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,14</t>
+          <t>-0,47; 0,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,46</t>
+          <t>-0,11; 0,46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; -0,05</t>
+          <t>-0,5; -0,05</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,21</t>
+          <t>-0,2; 0,31</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-30,04%</t>
+          <t>-17,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-7,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 324,15</t>
+          <t>-22,48; 342,78</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 71,2</t>
+          <t>-91,41; 50,28</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 263,85</t>
+          <t>-36,82; 292,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 144,62</t>
+          <t>-42,55; 144,21</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-89,02; 18,05</t>
+          <t>-89,73; 17,98</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 47,09</t>
+          <t>-60,28; 71,48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 149,22</t>
+          <t>-20,08; 149,96</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -5,29</t>
+          <t>-85,2; -15,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 64,82</t>
+          <t>-36,57; 104,59</t>
         </is>
       </c>
     </row>
